--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_11-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_11-12-2025.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>£9.69</t>
+          <t>£9.47</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -592,23 +592,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff775a78245
-	0x7ff775a782a0
-	0x7ff77585165d
-	0x7ff7758a9a33
-	0x7ff7758a9d3c
-	0x7ff7758fdf67
-	0x7ff7758fac97
-	0x7ff77589ac29
-	0x7ff77589ba93
-	0x7ff775d8ffe0
-	0x7ff775d8a920
-	0x7ff775da9086
-	0x7ff775a95744
-	0x7ff775a9e6ec
-	0x7ff775a81964
-	0x7ff775a81b15
-	0x7ff775a67842
+	0x7ff6c4be8245
+	0x7ff6c4be82a0
+	0x7ff6c49c165d
+	0x7ff6c4a19a33
+	0x7ff6c4a19d3c
+	0x7ff6c4a6df67
+	0x7ff6c4a6ac97
+	0x7ff6c4a0ac29
+	0x7ff6c4a0ba93
+	0x7ff6c4efffe0
+	0x7ff6c4efa920
+	0x7ff6c4f19086
+	0x7ff6c4c05744
+	0x7ff6c4c0e6ec
+	0x7ff6c4bf1964
+	0x7ff6c4bf1b15
+	0x7ff6c4bd7842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -712,23 +712,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff775a78245
-	0x7ff775a782a0
-	0x7ff77585165d
-	0x7ff7758a9a33
-	0x7ff7758a9d3c
-	0x7ff7758fdf67
-	0x7ff7758fac97
-	0x7ff77589ac29
-	0x7ff77589ba93
-	0x7ff775d8ffe0
-	0x7ff775d8a920
-	0x7ff775da9086
-	0x7ff775a95744
-	0x7ff775a9e6ec
-	0x7ff775a81964
-	0x7ff775a81b15
-	0x7ff775a67842
+	0x7ff6c4be8245
+	0x7ff6c4be82a0
+	0x7ff6c49c165d
+	0x7ff6c4a19a33
+	0x7ff6c4a19d3c
+	0x7ff6c4a6df67
+	0x7ff6c4a6ac97
+	0x7ff6c4a0ac29
+	0x7ff6c4a0ba93
+	0x7ff6c4efffe0
+	0x7ff6c4efa920
+	0x7ff6c4f19086
+	0x7ff6c4c05744
+	0x7ff6c4c0e6ec
+	0x7ff6c4bf1964
+	0x7ff6c4bf1b15
+	0x7ff6c4bd7842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -832,23 +832,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff775a78245
-	0x7ff775a782a0
-	0x7ff77585165d
-	0x7ff7758a9a33
-	0x7ff7758a9d3c
-	0x7ff7758fdf67
-	0x7ff7758fac97
-	0x7ff77589ac29
-	0x7ff77589ba93
-	0x7ff775d8ffe0
-	0x7ff775d8a920
-	0x7ff775da9086
-	0x7ff775a95744
-	0x7ff775a9e6ec
-	0x7ff775a81964
-	0x7ff775a81b15
-	0x7ff775a67842
+	0x7ff6c4be8245
+	0x7ff6c4be82a0
+	0x7ff6c49c165d
+	0x7ff6c4a19a33
+	0x7ff6c4a19d3c
+	0x7ff6c4a6df67
+	0x7ff6c4a6ac97
+	0x7ff6c4a0ac29
+	0x7ff6c4a0ba93
+	0x7ff6c4efffe0
+	0x7ff6c4efa920
+	0x7ff6c4f19086
+	0x7ff6c4c05744
+	0x7ff6c4c0e6ec
+	0x7ff6c4bf1964
+	0x7ff6c4bf1b15
+	0x7ff6c4bd7842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -928,7 +928,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>£14.68</t>
+          <t>£14.55</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -952,23 +952,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff775a78245
-	0x7ff775a782a0
-	0x7ff77585165d
-	0x7ff7758a9a33
-	0x7ff7758a9d3c
-	0x7ff7758fdf67
-	0x7ff7758fac97
-	0x7ff77589ac29
-	0x7ff77589ba93
-	0x7ff775d8ffe0
-	0x7ff775d8a920
-	0x7ff775da9086
-	0x7ff775a95744
-	0x7ff775a9e6ec
-	0x7ff775a81964
-	0x7ff775a81b15
-	0x7ff775a67842
+	0x7ff6c4be8245
+	0x7ff6c4be82a0
+	0x7ff6c49c165d
+	0x7ff6c4a19a33
+	0x7ff6c4a19d3c
+	0x7ff6c4a6df67
+	0x7ff6c4a6ac97
+	0x7ff6c4a0ac29
+	0x7ff6c4a0ba93
+	0x7ff6c4efffe0
+	0x7ff6c4efa920
+	0x7ff6c4f19086
+	0x7ff6c4c05744
+	0x7ff6c4c0e6ec
+	0x7ff6c4bf1964
+	0x7ff6c4bf1b15
+	0x7ff6c4bd7842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -1072,23 +1072,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff775a78245
-	0x7ff775a782a0
-	0x7ff77585165d
-	0x7ff7758a9a33
-	0x7ff7758a9d3c
-	0x7ff7758fdf67
-	0x7ff7758fac97
-	0x7ff77589ac29
-	0x7ff77589ba93
-	0x7ff775d8ffe0
-	0x7ff775d8a920
-	0x7ff775da9086
-	0x7ff775a95744
-	0x7ff775a9e6ec
-	0x7ff775a81964
-	0x7ff775a81b15
-	0x7ff775a67842
+	0x7ff6c4be8245
+	0x7ff6c4be82a0
+	0x7ff6c49c165d
+	0x7ff6c4a19a33
+	0x7ff6c4a19d3c
+	0x7ff6c4a6df67
+	0x7ff6c4a6ac97
+	0x7ff6c4a0ac29
+	0x7ff6c4a0ba93
+	0x7ff6c4efffe0
+	0x7ff6c4efa920
+	0x7ff6c4f19086
+	0x7ff6c4c05744
+	0x7ff6c4c0e6ec
+	0x7ff6c4bf1964
+	0x7ff6c4bf1b15
+	0x7ff6c4bd7842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -1192,23 +1192,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff775a78245
-	0x7ff775a782a0
-	0x7ff77585165d
-	0x7ff7758a9a33
-	0x7ff7758a9d3c
-	0x7ff7758fdf67
-	0x7ff7758fac97
-	0x7ff77589ac29
-	0x7ff77589ba93
-	0x7ff775d8ffe0
-	0x7ff775d8a920
-	0x7ff775da9086
-	0x7ff775a95744
-	0x7ff775a9e6ec
-	0x7ff775a81964
-	0x7ff775a81b15
-	0x7ff775a67842
+	0x7ff6c4be8245
+	0x7ff6c4be82a0
+	0x7ff6c49c165d
+	0x7ff6c4a19a33
+	0x7ff6c4a19d3c
+	0x7ff6c4a6df67
+	0x7ff6c4a6ac97
+	0x7ff6c4a0ac29
+	0x7ff6c4a0ba93
+	0x7ff6c4efffe0
+	0x7ff6c4efa920
+	0x7ff6c4f19086
+	0x7ff6c4c05744
+	0x7ff6c4c0e6ec
+	0x7ff6c4bf1964
+	0x7ff6c4bf1b15
+	0x7ff6c4bd7842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -1312,23 +1312,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff775a78245
-	0x7ff775a782a0
-	0x7ff77585165d
-	0x7ff7758a9a33
-	0x7ff7758a9d3c
-	0x7ff7758fdf67
-	0x7ff7758fac97
-	0x7ff77589ac29
-	0x7ff77589ba93
-	0x7ff775d8ffe0
-	0x7ff775d8a920
-	0x7ff775da9086
-	0x7ff775a95744
-	0x7ff775a9e6ec
-	0x7ff775a81964
-	0x7ff775a81b15
-	0x7ff775a67842
+	0x7ff6c4be8245
+	0x7ff6c4be82a0
+	0x7ff6c49c165d
+	0x7ff6c4a19a33
+	0x7ff6c4a19d3c
+	0x7ff6c4a6df67
+	0x7ff6c4a6ac97
+	0x7ff6c4a0ac29
+	0x7ff6c4a0ba93
+	0x7ff6c4efffe0
+	0x7ff6c4efa920
+	0x7ff6c4f19086
+	0x7ff6c4c05744
+	0x7ff6c4c0e6ec
+	0x7ff6c4bf1964
+	0x7ff6c4bf1b15
+	0x7ff6c4bd7842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -1432,23 +1432,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff775a78245
-	0x7ff775a782a0
-	0x7ff77585165d
-	0x7ff7758a9a33
-	0x7ff7758a9d3c
-	0x7ff7758fdf67
-	0x7ff7758fac97
-	0x7ff77589ac29
-	0x7ff77589ba93
-	0x7ff775d8ffe0
-	0x7ff775d8a920
-	0x7ff775da9086
-	0x7ff775a95744
-	0x7ff775a9e6ec
-	0x7ff775a81964
-	0x7ff775a81b15
-	0x7ff775a67842
+	0x7ff6c4be8245
+	0x7ff6c4be82a0
+	0x7ff6c49c165d
+	0x7ff6c4a19a33
+	0x7ff6c4a19d3c
+	0x7ff6c4a6df67
+	0x7ff6c4a6ac97
+	0x7ff6c4a0ac29
+	0x7ff6c4a0ba93
+	0x7ff6c4efffe0
+	0x7ff6c4efa920
+	0x7ff6c4f19086
+	0x7ff6c4c05744
+	0x7ff6c4c0e6ec
+	0x7ff6c4bf1964
+	0x7ff6c4bf1b15
+	0x7ff6c4bd7842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>£25.44</t>
+          <t>£24.95</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1552,23 +1552,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff775a78245
-	0x7ff775a782a0
-	0x7ff77585165d
-	0x7ff7758a9a33
-	0x7ff7758a9d3c
-	0x7ff7758fdf67
-	0x7ff7758fac97
-	0x7ff77589ac29
-	0x7ff77589ba93
-	0x7ff775d8ffe0
-	0x7ff775d8a920
-	0x7ff775da9086
-	0x7ff775a95744
-	0x7ff775a9e6ec
-	0x7ff775a81964
-	0x7ff775a81b15
-	0x7ff775a67842
+	0x7ff6c4be8245
+	0x7ff6c4be82a0
+	0x7ff6c49c165d
+	0x7ff6c4a19a33
+	0x7ff6c4a19d3c
+	0x7ff6c4a6df67
+	0x7ff6c4a6ac97
+	0x7ff6c4a0ac29
+	0x7ff6c4a0ba93
+	0x7ff6c4efffe0
+	0x7ff6c4efa920
+	0x7ff6c4f19086
+	0x7ff6c4c05744
+	0x7ff6c4c0e6ec
+	0x7ff6c4bf1964
+	0x7ff6c4bf1b15
+	0x7ff6c4bd7842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>£24.97</t>
+          <t>£24.38</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1672,23 +1672,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff775a78245
-	0x7ff775a782a0
-	0x7ff77585165d
-	0x7ff7758a9a33
-	0x7ff7758a9d3c
-	0x7ff7758fdf67
-	0x7ff7758fac97
-	0x7ff77589ac29
-	0x7ff77589ba93
-	0x7ff775d8ffe0
-	0x7ff775d8a920
-	0x7ff775da9086
-	0x7ff775a95744
-	0x7ff775a9e6ec
-	0x7ff775a81964
-	0x7ff775a81b15
-	0x7ff775a67842
+	0x7ff6c4be8245
+	0x7ff6c4be82a0
+	0x7ff6c49c165d
+	0x7ff6c4a19a33
+	0x7ff6c4a19d3c
+	0x7ff6c4a6df67
+	0x7ff6c4a6ac97
+	0x7ff6c4a0ac29
+	0x7ff6c4a0ba93
+	0x7ff6c4efffe0
+	0x7ff6c4efa920
+	0x7ff6c4f19086
+	0x7ff6c4c05744
+	0x7ff6c4c0e6ec
+	0x7ff6c4bf1964
+	0x7ff6c4bf1b15
+	0x7ff6c4bd7842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>£31.93</t>
+          <t>£30.69</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1792,23 +1792,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff775a78245
-	0x7ff775a782a0
-	0x7ff77585165d
-	0x7ff7758a9a33
-	0x7ff7758a9d3c
-	0x7ff7758fdf67
-	0x7ff7758fac97
-	0x7ff77589ac29
-	0x7ff77589ba93
-	0x7ff775d8ffe0
-	0x7ff775d8a920
-	0x7ff775da9086
-	0x7ff775a95744
-	0x7ff775a9e6ec
-	0x7ff775a81964
-	0x7ff775a81b15
-	0x7ff775a67842
+	0x7ff6c4be8245
+	0x7ff6c4be82a0
+	0x7ff6c49c165d
+	0x7ff6c4a19a33
+	0x7ff6c4a19d3c
+	0x7ff6c4a6df67
+	0x7ff6c4a6ac97
+	0x7ff6c4a0ac29
+	0x7ff6c4a0ba93
+	0x7ff6c4efffe0
+	0x7ff6c4efa920
+	0x7ff6c4f19086
+	0x7ff6c4c05744
+	0x7ff6c4c0e6ec
+	0x7ff6c4bf1964
+	0x7ff6c4bf1b15
+	0x7ff6c4bd7842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>£30.37</t>
+          <t>£30.27</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1912,23 +1912,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff775a78245
-	0x7ff775a782a0
-	0x7ff77585165d
-	0x7ff7758a9a33
-	0x7ff7758a9d3c
-	0x7ff7758fdf67
-	0x7ff7758fac97
-	0x7ff77589ac29
-	0x7ff77589ba93
-	0x7ff775d8ffe0
-	0x7ff775d8a920
-	0x7ff775da9086
-	0x7ff775a95744
-	0x7ff775a9e6ec
-	0x7ff775a81964
-	0x7ff775a81b15
-	0x7ff775a67842
+	0x7ff6c4be8245
+	0x7ff6c4be82a0
+	0x7ff6c49c165d
+	0x7ff6c4a19a33
+	0x7ff6c4a19d3c
+	0x7ff6c4a6df67
+	0x7ff6c4a6ac97
+	0x7ff6c4a0ac29
+	0x7ff6c4a0ba93
+	0x7ff6c4efffe0
+	0x7ff6c4efa920
+	0x7ff6c4f19086
+	0x7ff6c4c05744
+	0x7ff6c4c0e6ec
+	0x7ff6c4bf1964
+	0x7ff6c4bf1b15
+	0x7ff6c4bd7842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>£37.48</t>
+          <t>£37.00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2032,23 +2032,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff775a78245
-	0x7ff775a782a0
-	0x7ff77585165d
-	0x7ff7758a9a33
-	0x7ff7758a9d3c
-	0x7ff7758fdf67
-	0x7ff7758fac97
-	0x7ff77589ac29
-	0x7ff77589ba93
-	0x7ff775d8ffe0
-	0x7ff775d8a920
-	0x7ff775da9086
-	0x7ff775a95744
-	0x7ff775a9e6ec
-	0x7ff775a81964
-	0x7ff775a81b15
-	0x7ff775a67842
+	0x7ff6c4be8245
+	0x7ff6c4be82a0
+	0x7ff6c49c165d
+	0x7ff6c4a19a33
+	0x7ff6c4a19d3c
+	0x7ff6c4a6df67
+	0x7ff6c4a6ac97
+	0x7ff6c4a0ac29
+	0x7ff6c4a0ba93
+	0x7ff6c4efffe0
+	0x7ff6c4efa920
+	0x7ff6c4f19086
+	0x7ff6c4c05744
+	0x7ff6c4c0e6ec
+	0x7ff6c4bf1964
+	0x7ff6c4bf1b15
+	0x7ff6c4bd7842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -2152,23 +2152,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff775a78245
-	0x7ff775a782a0
-	0x7ff77585165d
-	0x7ff7758a9a33
-	0x7ff7758a9d3c
-	0x7ff7758fdf67
-	0x7ff7758fac97
-	0x7ff77589ac29
-	0x7ff77589ba93
-	0x7ff775d8ffe0
-	0x7ff775d8a920
-	0x7ff775da9086
-	0x7ff775a95744
-	0x7ff775a9e6ec
-	0x7ff775a81964
-	0x7ff775a81b15
-	0x7ff775a67842
+	0x7ff6c4be8245
+	0x7ff6c4be82a0
+	0x7ff6c49c165d
+	0x7ff6c4a19a33
+	0x7ff6c4a19d3c
+	0x7ff6c4a6df67
+	0x7ff6c4a6ac97
+	0x7ff6c4a0ac29
+	0x7ff6c4a0ba93
+	0x7ff6c4efffe0
+	0x7ff6c4efa920
+	0x7ff6c4f19086
+	0x7ff6c4c05744
+	0x7ff6c4c0e6ec
+	0x7ff6c4bf1964
+	0x7ff6c4bf1b15
+	0x7ff6c4bd7842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>£37.00</t>
+          <t>£36.83</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2272,23 +2272,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff775a78245
-	0x7ff775a782a0
-	0x7ff77585165d
-	0x7ff7758a9a33
-	0x7ff7758a9d3c
-	0x7ff7758fdf67
-	0x7ff7758fac97
-	0x7ff77589ac29
-	0x7ff77589ba93
-	0x7ff775d8ffe0
-	0x7ff775d8a920
-	0x7ff775da9086
-	0x7ff775a95744
-	0x7ff775a9e6ec
-	0x7ff775a81964
-	0x7ff775a81b15
-	0x7ff775a67842
+	0x7ff6c4be8245
+	0x7ff6c4be82a0
+	0x7ff6c49c165d
+	0x7ff6c4a19a33
+	0x7ff6c4a19d3c
+	0x7ff6c4a6df67
+	0x7ff6c4a6ac97
+	0x7ff6c4a0ac29
+	0x7ff6c4a0ba93
+	0x7ff6c4efffe0
+	0x7ff6c4efa920
+	0x7ff6c4f19086
+	0x7ff6c4c05744
+	0x7ff6c4c0e6ec
+	0x7ff6c4bf1964
+	0x7ff6c4bf1b15
+	0x7ff6c4bd7842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -2489,23 +2489,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff775a78245
-	0x7ff775a782a0
-	0x7ff77585165d
-	0x7ff7758a9a33
-	0x7ff7758a9d3c
-	0x7ff7758fdf67
-	0x7ff7758fac97
-	0x7ff77589ac29
-	0x7ff77589ba93
-	0x7ff775d8ffe0
-	0x7ff775d8a920
-	0x7ff775da9086
-	0x7ff775a95744
-	0x7ff775a9e6ec
-	0x7ff775a81964
-	0x7ff775a81b15
-	0x7ff775a67842
+	0x7ff6c4be8245
+	0x7ff6c4be82a0
+	0x7ff6c49c165d
+	0x7ff6c4a19a33
+	0x7ff6c4a19d3c
+	0x7ff6c4a6df67
+	0x7ff6c4a6ac97
+	0x7ff6c4a0ac29
+	0x7ff6c4a0ba93
+	0x7ff6c4efffe0
+	0x7ff6c4efa920
+	0x7ff6c4f19086
+	0x7ff6c4c05744
+	0x7ff6c4c0e6ec
+	0x7ff6c4bf1964
+	0x7ff6c4bf1b15
+	0x7ff6c4bd7842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -2609,23 +2609,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff775a78245
-	0x7ff775a782a0
-	0x7ff77585165d
-	0x7ff7758a9a33
-	0x7ff7758a9d3c
-	0x7ff7758fdf67
-	0x7ff7758fac97
-	0x7ff77589ac29
-	0x7ff77589ba93
-	0x7ff775d8ffe0
-	0x7ff775d8a920
-	0x7ff775da9086
-	0x7ff775a95744
-	0x7ff775a9e6ec
-	0x7ff775a81964
-	0x7ff775a81b15
-	0x7ff775a67842
+	0x7ff6c4be8245
+	0x7ff6c4be82a0
+	0x7ff6c49c165d
+	0x7ff6c4a19a33
+	0x7ff6c4a19d3c
+	0x7ff6c4a6df67
+	0x7ff6c4a6ac97
+	0x7ff6c4a0ac29
+	0x7ff6c4a0ba93
+	0x7ff6c4efffe0
+	0x7ff6c4efa920
+	0x7ff6c4f19086
+	0x7ff6c4c05744
+	0x7ff6c4c0e6ec
+	0x7ff6c4bf1964
+	0x7ff6c4bf1b15
+	0x7ff6c4bd7842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -2729,23 +2729,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff775a78245
-	0x7ff775a782a0
-	0x7ff77585165d
-	0x7ff7758a9a33
-	0x7ff7758a9d3c
-	0x7ff7758fdf67
-	0x7ff7758fac97
-	0x7ff77589ac29
-	0x7ff77589ba93
-	0x7ff775d8ffe0
-	0x7ff775d8a920
-	0x7ff775da9086
-	0x7ff775a95744
-	0x7ff775a9e6ec
-	0x7ff775a81964
-	0x7ff775a81b15
-	0x7ff775a67842
+	0x7ff6c4be8245
+	0x7ff6c4be82a0
+	0x7ff6c49c165d
+	0x7ff6c4a19a33
+	0x7ff6c4a19d3c
+	0x7ff6c4a6df67
+	0x7ff6c4a6ac97
+	0x7ff6c4a0ac29
+	0x7ff6c4a0ba93
+	0x7ff6c4efffe0
+	0x7ff6c4efa920
+	0x7ff6c4f19086
+	0x7ff6c4c05744
+	0x7ff6c4c0e6ec
+	0x7ff6c4bf1964
+	0x7ff6c4bf1b15
+	0x7ff6c4bd7842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -2849,23 +2849,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff775a78245
-	0x7ff775a782a0
-	0x7ff77585165d
-	0x7ff7758a9a33
-	0x7ff7758a9d3c
-	0x7ff7758fdf67
-	0x7ff7758fac97
-	0x7ff77589ac29
-	0x7ff77589ba93
-	0x7ff775d8ffe0
-	0x7ff775d8a920
-	0x7ff775da9086
-	0x7ff775a95744
-	0x7ff775a9e6ec
-	0x7ff775a81964
-	0x7ff775a81b15
-	0x7ff775a67842
+	0x7ff6c4be8245
+	0x7ff6c4be82a0
+	0x7ff6c49c165d
+	0x7ff6c4a19a33
+	0x7ff6c4a19d3c
+	0x7ff6c4a6df67
+	0x7ff6c4a6ac97
+	0x7ff6c4a0ac29
+	0x7ff6c4a0ba93
+	0x7ff6c4efffe0
+	0x7ff6c4efa920
+	0x7ff6c4f19086
+	0x7ff6c4c05744
+	0x7ff6c4c0e6ec
+	0x7ff6c4bf1964
+	0x7ff6c4bf1b15
+	0x7ff6c4bd7842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -2969,23 +2969,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff775a78245
-	0x7ff775a782a0
-	0x7ff77585165d
-	0x7ff7758a9a33
-	0x7ff7758a9d3c
-	0x7ff7758fdf67
-	0x7ff7758fac97
-	0x7ff77589ac29
-	0x7ff77589ba93
-	0x7ff775d8ffe0
-	0x7ff775d8a920
-	0x7ff775da9086
-	0x7ff775a95744
-	0x7ff775a9e6ec
-	0x7ff775a81964
-	0x7ff775a81b15
-	0x7ff775a67842
+	0x7ff6c4be8245
+	0x7ff6c4be82a0
+	0x7ff6c49c165d
+	0x7ff6c4a19a33
+	0x7ff6c4a19d3c
+	0x7ff6c4a6df67
+	0x7ff6c4a6ac97
+	0x7ff6c4a0ac29
+	0x7ff6c4a0ba93
+	0x7ff6c4efffe0
+	0x7ff6c4efa920
+	0x7ff6c4f19086
+	0x7ff6c4c05744
+	0x7ff6c4c0e6ec
+	0x7ff6c4bf1964
+	0x7ff6c4bf1b15
+	0x7ff6c4bd7842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -3089,23 +3089,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff775a78245
-	0x7ff775a782a0
-	0x7ff77585165d
-	0x7ff7758a9a33
-	0x7ff7758a9d3c
-	0x7ff7758fdf67
-	0x7ff7758fac97
-	0x7ff77589ac29
-	0x7ff77589ba93
-	0x7ff775d8ffe0
-	0x7ff775d8a920
-	0x7ff775da9086
-	0x7ff775a95744
-	0x7ff775a9e6ec
-	0x7ff775a81964
-	0x7ff775a81b15
-	0x7ff775a67842
+	0x7ff6c4be8245
+	0x7ff6c4be82a0
+	0x7ff6c49c165d
+	0x7ff6c4a19a33
+	0x7ff6c4a19d3c
+	0x7ff6c4a6df67
+	0x7ff6c4a6ac97
+	0x7ff6c4a0ac29
+	0x7ff6c4a0ba93
+	0x7ff6c4efffe0
+	0x7ff6c4efa920
+	0x7ff6c4f19086
+	0x7ff6c4c05744
+	0x7ff6c4c0e6ec
+	0x7ff6c4bf1964
+	0x7ff6c4bf1b15
+	0x7ff6c4bd7842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -3209,23 +3209,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff775a78245
-	0x7ff775a782a0
-	0x7ff77585165d
-	0x7ff7758a9a33
-	0x7ff7758a9d3c
-	0x7ff7758fdf67
-	0x7ff7758fac97
-	0x7ff77589ac29
-	0x7ff77589ba93
-	0x7ff775d8ffe0
-	0x7ff775d8a920
-	0x7ff775da9086
-	0x7ff775a95744
-	0x7ff775a9e6ec
-	0x7ff775a81964
-	0x7ff775a81b15
-	0x7ff775a67842
+	0x7ff6c4be8245
+	0x7ff6c4be82a0
+	0x7ff6c49c165d
+	0x7ff6c4a19a33
+	0x7ff6c4a19d3c
+	0x7ff6c4a6df67
+	0x7ff6c4a6ac97
+	0x7ff6c4a0ac29
+	0x7ff6c4a0ba93
+	0x7ff6c4efffe0
+	0x7ff6c4efa920
+	0x7ff6c4f19086
+	0x7ff6c4c05744
+	0x7ff6c4c0e6ec
+	0x7ff6c4bf1964
+	0x7ff6c4bf1b15
+	0x7ff6c4bd7842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -3329,23 +3329,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff775a78245
-	0x7ff775a782a0
-	0x7ff77585165d
-	0x7ff7758a9a33
-	0x7ff7758a9d3c
-	0x7ff7758fdf67
-	0x7ff7758fac97
-	0x7ff77589ac29
-	0x7ff77589ba93
-	0x7ff775d8ffe0
-	0x7ff775d8a920
-	0x7ff775da9086
-	0x7ff775a95744
-	0x7ff775a9e6ec
-	0x7ff775a81964
-	0x7ff775a81b15
-	0x7ff775a67842
+	0x7ff6c4be8245
+	0x7ff6c4be82a0
+	0x7ff6c49c165d
+	0x7ff6c4a19a33
+	0x7ff6c4a19d3c
+	0x7ff6c4a6df67
+	0x7ff6c4a6ac97
+	0x7ff6c4a0ac29
+	0x7ff6c4a0ba93
+	0x7ff6c4efffe0
+	0x7ff6c4efa920
+	0x7ff6c4f19086
+	0x7ff6c4c05744
+	0x7ff6c4c0e6ec
+	0x7ff6c4bf1964
+	0x7ff6c4bf1b15
+	0x7ff6c4bd7842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -3449,23 +3449,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff775a78245
-	0x7ff775a782a0
-	0x7ff77585165d
-	0x7ff7758a9a33
-	0x7ff7758a9d3c
-	0x7ff7758fdf67
-	0x7ff7758fac97
-	0x7ff77589ac29
-	0x7ff77589ba93
-	0x7ff775d8ffe0
-	0x7ff775d8a920
-	0x7ff775da9086
-	0x7ff775a95744
-	0x7ff775a9e6ec
-	0x7ff775a81964
-	0x7ff775a81b15
-	0x7ff775a67842
+	0x7ff6c4be8245
+	0x7ff6c4be82a0
+	0x7ff6c49c165d
+	0x7ff6c4a19a33
+	0x7ff6c4a19d3c
+	0x7ff6c4a6df67
+	0x7ff6c4a6ac97
+	0x7ff6c4a0ac29
+	0x7ff6c4a0ba93
+	0x7ff6c4efffe0
+	0x7ff6c4efa920
+	0x7ff6c4f19086
+	0x7ff6c4c05744
+	0x7ff6c4c0e6ec
+	0x7ff6c4bf1964
+	0x7ff6c4bf1b15
+	0x7ff6c4bd7842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
